--- a/data/batches/B11_Relationship_RELREC_SUPP/Test_Validation_Report/Test_Validation_Report_B11.xlsx
+++ b/data/batches/B11_Relationship_RELREC_SUPP/Test_Validation_Report/Test_Validation_Report_B11.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -8843,11 +8843,7 @@
           <t>RELREC</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>USUBJID</t>
@@ -8993,11 +8989,7 @@
           <t>RELREC</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>USUBJID</t>
@@ -9143,11 +9135,7 @@
           <t>RELREC</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>USUBJID</t>
@@ -9269,11 +9257,7 @@
           <t>RELREC</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -9395,11 +9379,7 @@
           <t>RELREC</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>USUBJID</t>
@@ -9545,11 +9525,7 @@
           <t>RELREC</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>USUBJID</t>
@@ -9952,11 +9928,7 @@
           <t>RELREC</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>IDVAR</t>
@@ -10948,11 +10920,7 @@
           <t>SUPPAE</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0019</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>QLABEL</t>
@@ -10979,11 +10947,7 @@
           <t>INCONSISTENT_QLABEL</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>Treatment Emergent Flag</t>
-        </is>
-      </c>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11006,7 +10970,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -11031,11 +10995,7 @@
           <t>SUPPAE</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0019</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>QLABEL</t>
@@ -11062,11 +11022,7 @@
           <t>INCONSISTENT_QLABEL</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>Treatment Emergent Flag</t>
-        </is>
-      </c>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11089,7 +11045,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -11114,11 +11070,7 @@
           <t>SUPPAE</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>BI-1245.110-MEX_SITE01-0019</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>QLABEL</t>
@@ -11145,11 +11097,7 @@
           <t>INCONSISTENT_QLABEL</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>Treatment Emergent Flag</t>
-        </is>
-      </c>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11172,7 +11120,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11168,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>USUBJID=BI-1245.110-RUS_SITE01-0011; count=31</t>
+          <t>Complete Row @ CSV Row 534; count=1</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -11230,12 +11178,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>USUBJID=BI-1245.110-RUS_SITE01-0011; count=33</t>
+          <t>Complete Row @ CSV Row 534; count=2</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -11245,17 +11193,17 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -11303,7 +11251,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>USUBJID=BI-1245.110-RUS_SITE01-0011; count=31</t>
+          <t>Complete Row @ CSV Row 511; count=1</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -11313,12 +11261,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>USUBJID=BI-1245.110-RUS_SITE01-0011; count=33</t>
+          <t>Complete Row @ CSV Row 511; count=2</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -11328,17 +11276,17 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>Duplicate row injection mismatch</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -11446,11 +11394,7 @@
           <t>SUPPAE</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>QNAM</t>
@@ -11477,11 +11421,7 @@
           <t>INCONSISTENT_QNAM</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>1BCDEFGH</t>
-        </is>
-      </c>
+      <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
           <t>No</t>
@@ -11504,7 +11444,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -11529,11 +11469,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>VSTPT</t>
@@ -11560,11 +11496,7 @@
           <t>90 MIN POST-DOSE</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>1H POST-DOSE</t>
-        </is>
-      </c>
+      <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11587,7 +11519,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -11612,11 +11544,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>BI-1245.110-USA_SITE01-0018</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>VSTPT</t>
@@ -11643,11 +11571,7 @@
           <t>90 MIN POST-DOSE</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>1H POST-DOSE</t>
-        </is>
-      </c>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11670,7 +11594,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -11695,11 +11619,7 @@
           <t>VS</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>BI-1245.110-KOR_SITE01-0012</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>VSTPT</t>
@@ -11726,11 +11646,7 @@
           <t>90 MIN POST-DOSE</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>1H POST-DOSE</t>
-        </is>
-      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11753,7 +11669,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -12350,7 +12266,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -12401,7 +12317,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -13341,10 +13257,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -13359,7 +13275,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>73.33</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
